--- a/Studio Anh Website FINAL/Lich Chup Thang 5.xlsx
+++ b/Studio Anh Website FINAL/Lich Chup Thang 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JackGK\Downloads\starter-kit\Studio Anh Website FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7442068-A7EE-4B20-94CF-4DC1FAD3F216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA128669-5457-4572-A951-8CAA07545B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="GoiChup" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LichChup!$G$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LichChup!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -842,6 +842,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
     <sortCondition ref="G1:G16"/>
   </sortState>
